--- a/scripts/seed-fournitures/referentiel_fournitures_par_classe.xlsx
+++ b/scripts/seed-fournitures/referentiel_fournitures_par_classe.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Articles uniques" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fournitures par classe'!$A$1:$J$837</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fournitures par classe'!$A$1:$J$865</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Articles uniques'!$A$1:$G$233</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J837"/>
+  <dimension ref="A1:J865"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
@@ -17367,7 +17367,7 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
@@ -17405,7 +17405,7 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
@@ -17481,7 +17481,7 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
@@ -17557,7 +17557,7 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
@@ -17595,7 +17595,7 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
@@ -17671,7 +17671,7 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
@@ -17747,7 +17747,7 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
@@ -17861,7 +17861,7 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
@@ -17899,7 +17899,7 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -18013,7 +18013,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
@@ -18127,7 +18127,7 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
@@ -18165,7 +18165,7 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
@@ -18241,7 +18241,7 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
@@ -18279,7 +18279,7 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
@@ -18393,7 +18393,7 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
@@ -18469,7 +18469,7 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
@@ -18507,7 +18507,7 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
@@ -18545,7 +18545,7 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
@@ -18621,7 +18621,7 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
@@ -18659,7 +18659,7 @@
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
@@ -18773,7 +18773,7 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
@@ -18887,7 +18887,7 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
@@ -19001,7 +19001,7 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
@@ -19115,7 +19115,7 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
@@ -19153,7 +19153,7 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
@@ -19267,7 +19267,7 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
@@ -19343,7 +19343,7 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
@@ -19381,7 +19381,7 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
@@ -19419,7 +19419,7 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
@@ -19495,7 +19495,7 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
@@ -19609,7 +19609,7 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
@@ -19685,7 +19685,7 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
@@ -19723,7 +19723,7 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
@@ -19761,7 +19761,7 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
@@ -19837,7 +19837,7 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
@@ -19913,7 +19913,7 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
@@ -20027,7 +20027,7 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
@@ -20065,7 +20065,7 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
@@ -20103,7 +20103,7 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
@@ -20217,7 +20217,7 @@
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
@@ -20331,7 +20331,7 @@
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
@@ -20369,7 +20369,7 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
@@ -20407,7 +20407,7 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
@@ -20483,7 +20483,7 @@
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
@@ -20521,7 +20521,7 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
@@ -20559,7 +20559,7 @@
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
@@ -20673,7 +20673,7 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
@@ -20711,7 +20711,7 @@
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
@@ -20825,7 +20825,7 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
@@ -20863,7 +20863,7 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
@@ -20901,7 +20901,7 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
@@ -20977,7 +20977,7 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
@@ -21129,7 +21129,7 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
@@ -21205,7 +21205,7 @@
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="C541" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D541" s="2" t="inlineStr">
@@ -21281,7 +21281,7 @@
       </c>
       <c r="C542" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="C543" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D543" s="2" t="inlineStr">
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C544" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D544" s="2" t="inlineStr">
@@ -21395,7 +21395,7 @@
       </c>
       <c r="C545" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D545" s="2" t="inlineStr">
@@ -21433,7 +21433,7 @@
       </c>
       <c r="C546" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D546" s="2" t="inlineStr">
@@ -21471,7 +21471,7 @@
       </c>
       <c r="C547" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D547" s="2" t="inlineStr">
@@ -21509,7 +21509,7 @@
       </c>
       <c r="C548" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D548" s="2" t="inlineStr">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="C549" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D549" s="2" t="inlineStr">
@@ -21585,7 +21585,7 @@
       </c>
       <c r="C550" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr">
@@ -21623,7 +21623,7 @@
       </c>
       <c r="C551" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D551" s="2" t="inlineStr">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="C552" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D552" s="2" t="inlineStr">
@@ -21699,7 +21699,7 @@
       </c>
       <c r="C553" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D553" s="2" t="inlineStr">
@@ -21737,7 +21737,7 @@
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
@@ -21775,7 +21775,7 @@
       </c>
       <c r="C555" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D555" s="2" t="inlineStr">
@@ -21813,7 +21813,7 @@
       </c>
       <c r="C556" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D556" s="2" t="inlineStr">
@@ -21851,7 +21851,7 @@
       </c>
       <c r="C557" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D557" s="2" t="inlineStr">
@@ -21889,7 +21889,7 @@
       </c>
       <c r="C558" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D558" s="2" t="inlineStr">
@@ -21927,7 +21927,7 @@
       </c>
       <c r="C559" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D559" s="2" t="inlineStr">
@@ -21965,7 +21965,7 @@
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
@@ -22003,7 +22003,7 @@
       </c>
       <c r="C561" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D561" s="2" t="inlineStr">
@@ -22041,7 +22041,7 @@
       </c>
       <c r="C562" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr">
@@ -22079,7 +22079,7 @@
       </c>
       <c r="C563" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D563" s="2" t="inlineStr">
@@ -22117,7 +22117,7 @@
       </c>
       <c r="C564" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr">
@@ -22155,7 +22155,7 @@
       </c>
       <c r="C565" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D565" s="2" t="inlineStr">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="C566" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D566" s="2" t="inlineStr">
@@ -22231,7 +22231,7 @@
       </c>
       <c r="C567" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D567" s="2" t="inlineStr">
@@ -22269,7 +22269,7 @@
       </c>
       <c r="C568" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D568" s="2" t="inlineStr">
@@ -22307,7 +22307,7 @@
       </c>
       <c r="C569" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D569" s="2" t="inlineStr">
@@ -22345,7 +22345,7 @@
       </c>
       <c r="C570" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D570" s="2" t="inlineStr">
@@ -22383,7 +22383,7 @@
       </c>
       <c r="C571" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D571" s="2" t="inlineStr">
@@ -22421,7 +22421,7 @@
       </c>
       <c r="C572" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D572" s="2" t="inlineStr">
@@ -22459,7 +22459,7 @@
       </c>
       <c r="C573" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D573" s="2" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="C574" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D574" s="2" t="inlineStr">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="C575" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D575" s="2" t="inlineStr">
@@ -22573,7 +22573,7 @@
       </c>
       <c r="C576" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D576" s="2" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="C577" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D577" s="2" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="C578" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D578" s="2" t="inlineStr">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="C579" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D579" s="2" t="inlineStr">
@@ -22725,7 +22725,7 @@
       </c>
       <c r="C580" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D580" s="2" t="inlineStr">
@@ -22763,7 +22763,7 @@
       </c>
       <c r="C581" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D581" s="2" t="inlineStr">
@@ -22801,7 +22801,7 @@
       </c>
       <c r="C582" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D582" s="2" t="inlineStr">
@@ -22839,7 +22839,7 @@
       </c>
       <c r="C583" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D583" s="2" t="inlineStr">
@@ -22877,7 +22877,7 @@
       </c>
       <c r="C584" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D584" s="2" t="inlineStr">
@@ -22915,7 +22915,7 @@
       </c>
       <c r="C585" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D585" s="2" t="inlineStr">
@@ -22953,7 +22953,7 @@
       </c>
       <c r="C586" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D586" s="2" t="inlineStr">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="C587" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D587" s="2" t="inlineStr">
@@ -23029,7 +23029,7 @@
       </c>
       <c r="C588" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D588" s="2" t="inlineStr">
@@ -23067,7 +23067,7 @@
       </c>
       <c r="C589" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D589" s="2" t="inlineStr">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="C590" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D590" s="2" t="inlineStr">
@@ -23143,7 +23143,7 @@
       </c>
       <c r="C591" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D591" s="2" t="inlineStr">
@@ -23181,7 +23181,7 @@
       </c>
       <c r="C592" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D592" s="2" t="inlineStr">
@@ -23219,7 +23219,7 @@
       </c>
       <c r="C593" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D593" s="2" t="inlineStr">
@@ -23257,7 +23257,7 @@
       </c>
       <c r="C594" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D594" s="2" t="inlineStr">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="C595" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D595" s="2" t="inlineStr">
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C596" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D596" s="2" t="inlineStr">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="C597" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D597" s="2" t="inlineStr">
@@ -23409,7 +23409,7 @@
       </c>
       <c r="C598" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D598" s="2" t="inlineStr">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="C599" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D599" s="2" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="C600" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D600" s="2" t="inlineStr">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="C601" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D601" s="2" t="inlineStr">
@@ -23561,7 +23561,7 @@
       </c>
       <c r="C602" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D602" s="2" t="inlineStr">
@@ -23599,7 +23599,7 @@
       </c>
       <c r="C603" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D603" s="2" t="inlineStr">
@@ -23637,7 +23637,7 @@
       </c>
       <c r="C604" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D604" s="2" t="inlineStr">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="C605" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D605" s="2" t="inlineStr">
@@ -23713,7 +23713,7 @@
       </c>
       <c r="C606" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D606" s="2" t="inlineStr">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="C607" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D607" s="2" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="C608" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D608" s="2" t="inlineStr">
@@ -23827,7 +23827,7 @@
       </c>
       <c r="C609" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D609" s="2" t="inlineStr">
@@ -23865,7 +23865,7 @@
       </c>
       <c r="C610" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D610" s="2" t="inlineStr">
@@ -23903,7 +23903,7 @@
       </c>
       <c r="C611" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D611" s="2" t="inlineStr">
@@ -23941,7 +23941,7 @@
       </c>
       <c r="C612" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D612" s="2" t="inlineStr">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="C613" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D613" s="2" t="inlineStr">
@@ -24017,7 +24017,7 @@
       </c>
       <c r="C614" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D614" s="2" t="inlineStr">
@@ -24055,7 +24055,7 @@
       </c>
       <c r="C615" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D615" s="2" t="inlineStr">
@@ -24093,7 +24093,7 @@
       </c>
       <c r="C616" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D616" s="2" t="inlineStr">
@@ -24131,7 +24131,7 @@
       </c>
       <c r="C617" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D617" s="2" t="inlineStr">
@@ -24169,7 +24169,7 @@
       </c>
       <c r="C618" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D618" s="2" t="inlineStr">
@@ -24207,7 +24207,7 @@
       </c>
       <c r="C619" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D619" s="2" t="inlineStr">
@@ -24245,7 +24245,7 @@
       </c>
       <c r="C620" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D620" s="2" t="inlineStr">
@@ -24283,7 +24283,7 @@
       </c>
       <c r="C621" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D621" s="2" t="inlineStr">
@@ -24321,7 +24321,7 @@
       </c>
       <c r="C622" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D622" s="2" t="inlineStr">
@@ -24359,7 +24359,7 @@
       </c>
       <c r="C623" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D623" s="2" t="inlineStr">
@@ -24397,7 +24397,7 @@
       </c>
       <c r="C624" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D624" s="2" t="inlineStr">
@@ -24435,7 +24435,7 @@
       </c>
       <c r="C625" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D625" s="2" t="inlineStr">
@@ -24473,7 +24473,7 @@
       </c>
       <c r="C626" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D626" s="2" t="inlineStr">
@@ -24511,7 +24511,7 @@
       </c>
       <c r="C627" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D627" s="2" t="inlineStr">
@@ -24549,7 +24549,7 @@
       </c>
       <c r="C628" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D628" s="2" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="C629" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D629" s="2" t="inlineStr">
@@ -24625,7 +24625,7 @@
       </c>
       <c r="C630" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D630" s="2" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="C631" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D631" s="2" t="inlineStr">
@@ -24701,7 +24701,7 @@
       </c>
       <c r="C632" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D632" s="2" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="C633" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D633" s="2" t="inlineStr">
@@ -24777,7 +24777,7 @@
       </c>
       <c r="C634" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D634" s="2" t="inlineStr">
@@ -24815,7 +24815,7 @@
       </c>
       <c r="C635" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D635" s="2" t="inlineStr">
@@ -24853,7 +24853,7 @@
       </c>
       <c r="C636" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D636" s="2" t="inlineStr">
@@ -24891,7 +24891,7 @@
       </c>
       <c r="C637" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D637" s="2" t="inlineStr">
@@ -24929,7 +24929,7 @@
       </c>
       <c r="C638" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D638" s="2" t="inlineStr">
@@ -24967,7 +24967,7 @@
       </c>
       <c r="C639" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D639" s="2" t="inlineStr">
@@ -25005,7 +25005,7 @@
       </c>
       <c r="C640" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D640" s="2" t="inlineStr">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C641" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D641" s="2" t="inlineStr">
@@ -25081,7 +25081,7 @@
       </c>
       <c r="C642" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D642" s="2" t="inlineStr">
@@ -25119,7 +25119,7 @@
       </c>
       <c r="C643" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D643" s="2" t="inlineStr">
@@ -25157,7 +25157,7 @@
       </c>
       <c r="C644" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D644" s="2" t="inlineStr">
@@ -25195,7 +25195,7 @@
       </c>
       <c r="C645" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D645" s="2" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="C646" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D646" s="2" t="inlineStr">
@@ -25271,7 +25271,7 @@
       </c>
       <c r="C647" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D647" s="2" t="inlineStr">
@@ -25309,7 +25309,7 @@
       </c>
       <c r="C648" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D648" s="2" t="inlineStr">
@@ -25347,7 +25347,7 @@
       </c>
       <c r="C649" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D649" s="2" t="inlineStr">
@@ -25385,7 +25385,7 @@
       </c>
       <c r="C650" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D650" s="2" t="inlineStr">
@@ -25423,7 +25423,7 @@
       </c>
       <c r="C651" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D651" s="2" t="inlineStr">
@@ -25461,7 +25461,7 @@
       </c>
       <c r="C652" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D652" s="2" t="inlineStr">
@@ -25499,7 +25499,7 @@
       </c>
       <c r="C653" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D653" s="2" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="C654" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D654" s="2" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C655" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D655" s="2" t="inlineStr">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C656" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D656" s="2" t="inlineStr">
@@ -25651,7 +25651,7 @@
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
@@ -25689,7 +25689,7 @@
       </c>
       <c r="C658" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D658" s="2" t="inlineStr">
@@ -25727,7 +25727,7 @@
       </c>
       <c r="C659" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D659" s="2" t="inlineStr">
@@ -25765,7 +25765,7 @@
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
@@ -25879,7 +25879,7 @@
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -25955,7 +25955,7 @@
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
@@ -25993,7 +25993,7 @@
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
@@ -26031,7 +26031,7 @@
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
@@ -26069,7 +26069,7 @@
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
@@ -26107,7 +26107,7 @@
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
@@ -26145,7 +26145,7 @@
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
@@ -26183,7 +26183,7 @@
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="C672" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D672" s="2" t="inlineStr">
@@ -26259,7 +26259,7 @@
       </c>
       <c r="C673" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D673" s="2" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
@@ -26335,7 +26335,7 @@
       </c>
       <c r="C675" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D675" s="2" t="inlineStr">
@@ -26373,7 +26373,7 @@
       </c>
       <c r="C676" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D676" s="2" t="inlineStr">
@@ -26411,7 +26411,7 @@
       </c>
       <c r="C677" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D677" s="2" t="inlineStr">
@@ -26449,7 +26449,7 @@
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
@@ -26487,7 +26487,7 @@
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
@@ -26525,7 +26525,7 @@
       </c>
       <c r="C680" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D680" s="2" t="inlineStr">
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C681" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D681" s="2" t="inlineStr">
@@ -26601,7 +26601,7 @@
       </c>
       <c r="C682" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D682" s="2" t="inlineStr">
@@ -26639,7 +26639,7 @@
       </c>
       <c r="C683" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D683" s="2" t="inlineStr">
@@ -26677,7 +26677,7 @@
       </c>
       <c r="C684" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D684" s="2" t="inlineStr">
@@ -26715,7 +26715,7 @@
       </c>
       <c r="C685" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D685" s="2" t="inlineStr">
@@ -26753,7 +26753,7 @@
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
@@ -26791,7 +26791,7 @@
       </c>
       <c r="C687" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D687" s="2" t="inlineStr">
@@ -26829,7 +26829,7 @@
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
@@ -26867,7 +26867,7 @@
       </c>
       <c r="C689" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D689" s="2" t="inlineStr">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="C690" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D690" s="2" t="inlineStr">
@@ -26943,7 +26943,7 @@
       </c>
       <c r="C691" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D691" s="2" t="inlineStr">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="C692" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D692" s="2" t="inlineStr">
@@ -27019,7 +27019,7 @@
       </c>
       <c r="C693" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D693" s="2" t="inlineStr">
@@ -27057,7 +27057,7 @@
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
@@ -27095,7 +27095,7 @@
       </c>
       <c r="C695" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D695" s="2" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
@@ -27171,7 +27171,7 @@
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
@@ -27209,7 +27209,7 @@
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
@@ -27247,7 +27247,7 @@
       </c>
       <c r="C699" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D699" s="2" t="inlineStr">
@@ -27285,7 +27285,7 @@
       </c>
       <c r="C700" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D700" s="2" t="inlineStr">
@@ -27323,7 +27323,7 @@
       </c>
       <c r="C701" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D701" s="2" t="inlineStr">
@@ -27361,7 +27361,7 @@
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
@@ -27399,7 +27399,7 @@
       </c>
       <c r="C703" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D703" s="2" t="inlineStr">
@@ -27437,7 +27437,7 @@
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -27475,7 +27475,7 @@
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -27513,7 +27513,7 @@
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
@@ -27551,7 +27551,7 @@
       </c>
       <c r="C707" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D707" s="2" t="inlineStr">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="C708" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D708" s="2" t="inlineStr">
@@ -27627,7 +27627,7 @@
       </c>
       <c r="C709" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D709" s="2" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="C710" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D710" s="2" t="inlineStr">
@@ -27703,7 +27703,7 @@
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D711" s="2" t="inlineStr">
@@ -27741,7 +27741,7 @@
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
@@ -27779,7 +27779,7 @@
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D713" s="2" t="inlineStr">
@@ -27817,7 +27817,7 @@
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
@@ -27855,7 +27855,7 @@
       </c>
       <c r="C715" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D715" s="2" t="inlineStr">
@@ -27893,7 +27893,7 @@
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -27931,7 +27931,7 @@
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -27969,7 +27969,7 @@
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="C719" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D719" s="2" t="inlineStr">
@@ -28045,7 +28045,7 @@
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
@@ -28083,7 +28083,7 @@
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
@@ -28159,7 +28159,7 @@
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -28197,7 +28197,7 @@
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -28235,7 +28235,7 @@
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
@@ -28273,7 +28273,7 @@
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -28311,7 +28311,7 @@
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
@@ -28387,7 +28387,7 @@
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D729" s="2" t="inlineStr">
@@ -28425,7 +28425,7 @@
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
@@ -28463,7 +28463,7 @@
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -28501,7 +28501,7 @@
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -28539,7 +28539,7 @@
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -28577,7 +28577,7 @@
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -28615,7 +28615,7 @@
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -28653,7 +28653,7 @@
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -28691,7 +28691,7 @@
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -28767,7 +28767,7 @@
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -28805,7 +28805,7 @@
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -28843,7 +28843,7 @@
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -28881,7 +28881,7 @@
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -28919,7 +28919,7 @@
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -28957,7 +28957,7 @@
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -28995,7 +28995,7 @@
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -29033,7 +29033,7 @@
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -29071,7 +29071,7 @@
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -29109,7 +29109,7 @@
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -29147,7 +29147,7 @@
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
@@ -29185,7 +29185,7 @@
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D750" s="2" t="inlineStr">
@@ -29223,7 +29223,7 @@
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
@@ -29261,7 +29261,7 @@
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -29299,7 +29299,7 @@
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
@@ -29337,7 +29337,7 @@
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
@@ -29375,7 +29375,7 @@
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D755" s="2" t="inlineStr">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
@@ -29451,7 +29451,7 @@
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
@@ -29489,7 +29489,7 @@
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
@@ -29527,7 +29527,7 @@
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -29565,7 +29565,7 @@
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
@@ -29603,7 +29603,7 @@
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
@@ -29641,7 +29641,7 @@
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -29717,7 +29717,7 @@
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D764" s="2" t="inlineStr">
@@ -29755,7 +29755,7 @@
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -29793,7 +29793,7 @@
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -29831,7 +29831,7 @@
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -29869,7 +29869,7 @@
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -29907,7 +29907,7 @@
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -29945,7 +29945,7 @@
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -29983,7 +29983,7 @@
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -30021,7 +30021,7 @@
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -30059,7 +30059,7 @@
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -30097,7 +30097,7 @@
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -30173,7 +30173,7 @@
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -30211,7 +30211,7 @@
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -30249,7 +30249,7 @@
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -30287,7 +30287,7 @@
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
@@ -30325,7 +30325,7 @@
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -30363,7 +30363,7 @@
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -30401,7 +30401,7 @@
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -30477,7 +30477,7 @@
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -30515,7 +30515,7 @@
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -30553,7 +30553,7 @@
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -30591,7 +30591,7 @@
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -30629,7 +30629,7 @@
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -30667,7 +30667,7 @@
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -30705,7 +30705,7 @@
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
@@ -30743,7 +30743,7 @@
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
@@ -30781,7 +30781,7 @@
       </c>
       <c r="C792" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D792" s="2" t="inlineStr">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C793" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D793" s="2" t="inlineStr">
@@ -30857,7 +30857,7 @@
       </c>
       <c r="C794" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D794" s="2" t="inlineStr">
@@ -30895,7 +30895,7 @@
       </c>
       <c r="C795" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D795" s="2" t="inlineStr">
@@ -30933,7 +30933,7 @@
       </c>
       <c r="C796" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D796" s="2" t="inlineStr">
@@ -30971,7 +30971,7 @@
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
@@ -31009,7 +31009,7 @@
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -31047,7 +31047,7 @@
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
@@ -31085,7 +31085,7 @@
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -31123,7 +31123,7 @@
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -31161,7 +31161,7 @@
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -31199,7 +31199,7 @@
       </c>
       <c r="C803" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D803" s="2" t="inlineStr">
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C804" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D804" s="2" t="inlineStr">
@@ -31275,7 +31275,7 @@
       </c>
       <c r="C805" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D805" s="2" t="inlineStr">
@@ -31313,7 +31313,7 @@
       </c>
       <c r="C806" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D806" s="2" t="inlineStr">
@@ -31351,7 +31351,7 @@
       </c>
       <c r="C807" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D807" s="2" t="inlineStr">
@@ -31389,7 +31389,7 @@
       </c>
       <c r="C808" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D808" s="2" t="inlineStr">
@@ -31427,7 +31427,7 @@
       </c>
       <c r="C809" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D809" s="2" t="inlineStr">
@@ -31465,12 +31465,12 @@
       </c>
       <c r="C810" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D810" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E810" s="2" t="inlineStr">
@@ -31503,12 +31503,12 @@
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E811" s="2" t="inlineStr">
@@ -31541,12 +31541,12 @@
       </c>
       <c r="C812" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D812" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E812" s="2" t="inlineStr">
@@ -31579,12 +31579,12 @@
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E813" s="2" t="inlineStr">
@@ -31617,12 +31617,12 @@
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E814" s="2" t="inlineStr">
@@ -31655,12 +31655,12 @@
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E815" s="2" t="inlineStr">
@@ -31693,12 +31693,12 @@
       </c>
       <c r="C816" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D816" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E816" s="2" t="inlineStr">
@@ -31731,12 +31731,12 @@
       </c>
       <c r="C817" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D817" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E817" s="2" t="inlineStr">
@@ -31769,12 +31769,12 @@
       </c>
       <c r="C818" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D818" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E818" s="2" t="inlineStr">
@@ -31807,12 +31807,12 @@
       </c>
       <c r="C819" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D819" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E819" s="2" t="inlineStr">
@@ -31845,12 +31845,12 @@
       </c>
       <c r="C820" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D820" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E820" s="2" t="inlineStr">
@@ -31883,12 +31883,12 @@
       </c>
       <c r="C821" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D821" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E821" s="2" t="inlineStr">
@@ -31921,12 +31921,12 @@
       </c>
       <c r="C822" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D822" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E822" s="2" t="inlineStr">
@@ -31959,12 +31959,12 @@
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E823" s="2" t="inlineStr">
@@ -31997,12 +31997,12 @@
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E824" s="2" t="inlineStr">
@@ -32035,12 +32035,12 @@
       </c>
       <c r="C825" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D825" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E825" s="2" t="inlineStr">
@@ -32073,12 +32073,12 @@
       </c>
       <c r="C826" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D826" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E826" s="2" t="inlineStr">
@@ -32111,12 +32111,12 @@
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E827" s="2" t="inlineStr">
@@ -32149,12 +32149,12 @@
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E828" s="2" t="inlineStr">
@@ -32187,12 +32187,12 @@
       </c>
       <c r="C829" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D829" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E829" s="2" t="inlineStr">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E830" s="2" t="inlineStr">
@@ -32263,12 +32263,12 @@
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E831" s="2" t="inlineStr">
@@ -32301,12 +32301,12 @@
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E832" s="2" t="inlineStr">
@@ -32339,12 +32339,12 @@
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E833" s="2" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E834" s="2" t="inlineStr">
@@ -32415,12 +32415,12 @@
       </c>
       <c r="C835" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D835" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E835" s="2" t="inlineStr">
@@ -32453,12 +32453,12 @@
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E836" s="2" t="inlineStr">
@@ -32491,12 +32491,12 @@
       </c>
       <c r="C837" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="D837" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="E837" s="2" t="inlineStr">
@@ -32516,8 +32516,1072 @@
       <c r="I837" s="2" t="inlineStr"/>
       <c r="J837" s="2" t="inlineStr"/>
     </row>
+    <row r="838">
+      <c r="A838" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B838" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C838" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D838" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E838" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F838" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines 500 leaves Ledger A4 (English Language)</t>
+        </is>
+      </c>
+      <c r="G838" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H838" s="2" t="inlineStr"/>
+      <c r="I838" s="2" t="inlineStr"/>
+      <c r="J838" s="2" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B839" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C839" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D839" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E839" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F839" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines 500 leaves Ledger A4 (French)</t>
+        </is>
+      </c>
+      <c r="G839" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H839" s="2" t="inlineStr"/>
+      <c r="I839" s="2" t="inlineStr"/>
+      <c r="J839" s="2" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B840" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C840" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D840" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E840" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F840" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines 500 leaves Ledger A4 (Literature)</t>
+        </is>
+      </c>
+      <c r="G840" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H840" s="2" t="inlineStr"/>
+      <c r="I840" s="2" t="inlineStr"/>
+      <c r="J840" s="2" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B841" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C841" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D841" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E841" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F841" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines 500 leaves Ledger A4 (Geography)</t>
+        </is>
+      </c>
+      <c r="G841" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H841" s="2" t="inlineStr"/>
+      <c r="I841" s="2" t="inlineStr"/>
+      <c r="J841" s="2" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B842" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D842" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E842" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F842" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines 80 leaves A5 (Geography)</t>
+        </is>
+      </c>
+      <c r="G842" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H842" s="2" t="inlineStr"/>
+      <c r="I842" s="2" t="inlineStr"/>
+      <c r="J842" s="2" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B843" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C843" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D843" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E843" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F843" s="2" t="inlineStr">
+        <is>
+          <t>Graph book (Geography)</t>
+        </is>
+      </c>
+      <c r="G843" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H843" s="2" t="inlineStr"/>
+      <c r="I843" s="2" t="inlineStr"/>
+      <c r="J843" s="2" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B844" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D844" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E844" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F844" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines 500 leaves Ledger A4 (History)</t>
+        </is>
+      </c>
+      <c r="G844" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H844" s="2" t="inlineStr"/>
+      <c r="I844" s="2" t="inlineStr"/>
+      <c r="J844" s="2" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B845" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C845" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D845" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E845" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F845" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines 500 leaves Ledger A4 (Philosophy)</t>
+        </is>
+      </c>
+      <c r="G845" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H845" s="2" t="inlineStr"/>
+      <c r="I845" s="2" t="inlineStr"/>
+      <c r="J845" s="2" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B846" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D846" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E846" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F846" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines Ledger 500 pages (Pure Mathematics)</t>
+        </is>
+      </c>
+      <c r="G846" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H846" s="2" t="inlineStr"/>
+      <c r="I846" s="2" t="inlineStr"/>
+      <c r="J846" s="2" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B847" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C847" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D847" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E847" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F847" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines Ledger 500 pages (Mechanics)</t>
+        </is>
+      </c>
+      <c r="G847" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H847" s="2" t="inlineStr"/>
+      <c r="I847" s="2" t="inlineStr"/>
+      <c r="J847" s="2" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B848" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D848" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E848" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F848" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines Ledger 500 pages (Chemistry)</t>
+        </is>
+      </c>
+      <c r="G848" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H848" s="2" t="inlineStr"/>
+      <c r="I848" s="2" t="inlineStr"/>
+      <c r="J848" s="2" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B849" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C849" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D849" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E849" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F849" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines Ledger 500 pages (Biology)</t>
+        </is>
+      </c>
+      <c r="G849" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H849" s="2" t="inlineStr"/>
+      <c r="I849" s="2" t="inlineStr"/>
+      <c r="J849" s="2" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B850" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D850" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E850" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F850" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines Ledger 500 pages (Physics)</t>
+        </is>
+      </c>
+      <c r="G850" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H850" s="2" t="inlineStr"/>
+      <c r="I850" s="2" t="inlineStr"/>
+      <c r="J850" s="2" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B851" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C851" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D851" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E851" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F851" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines Ledger 500 pages (ICT)</t>
+        </is>
+      </c>
+      <c r="G851" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H851" s="2" t="inlineStr"/>
+      <c r="I851" s="2" t="inlineStr"/>
+      <c r="J851" s="2" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B852" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D852" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E852" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F852" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines Ledger 500 pages (Computer Science)</t>
+        </is>
+      </c>
+      <c r="G852" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H852" s="2" t="inlineStr"/>
+      <c r="I852" s="2" t="inlineStr"/>
+      <c r="J852" s="2" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B853" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C853" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D853" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E853" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F853" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines Ledger 500 pages (Economics)</t>
+        </is>
+      </c>
+      <c r="G853" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H853" s="2" t="inlineStr"/>
+      <c r="I853" s="2" t="inlineStr"/>
+      <c r="J853" s="2" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B854" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C854" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D854" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E854" s="2" t="inlineStr">
+        <is>
+          <t>Cahier</t>
+        </is>
+      </c>
+      <c r="F854" s="2" t="inlineStr">
+        <is>
+          <t>Plain lines Ledger 500 pages (Statistics)</t>
+        </is>
+      </c>
+      <c r="G854" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H854" s="2" t="inlineStr"/>
+      <c r="I854" s="2" t="inlineStr"/>
+      <c r="J854" s="2" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B855" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C855" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D855" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E855" s="2" t="inlineStr">
+        <is>
+          <t>Écriture</t>
+        </is>
+      </c>
+      <c r="F855" s="2" t="inlineStr">
+        <is>
+          <t>Stylo bleu</t>
+        </is>
+      </c>
+      <c r="G855" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H855" s="2" t="inlineStr"/>
+      <c r="I855" s="2" t="inlineStr"/>
+      <c r="J855" s="2" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B856" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C856" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D856" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E856" s="2" t="inlineStr">
+        <is>
+          <t>Écriture</t>
+        </is>
+      </c>
+      <c r="F856" s="2" t="inlineStr">
+        <is>
+          <t>Stylo rouge</t>
+        </is>
+      </c>
+      <c r="G856" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H856" s="2" t="inlineStr"/>
+      <c r="I856" s="2" t="inlineStr"/>
+      <c r="J856" s="2" t="inlineStr"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B857" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C857" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D857" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E857" s="2" t="inlineStr">
+        <is>
+          <t>Écriture</t>
+        </is>
+      </c>
+      <c r="F857" s="2" t="inlineStr">
+        <is>
+          <t>Stylo noir</t>
+        </is>
+      </c>
+      <c r="G857" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H857" s="2" t="inlineStr"/>
+      <c r="I857" s="2" t="inlineStr"/>
+      <c r="J857" s="2" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B858" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C858" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D858" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E858" s="2" t="inlineStr">
+        <is>
+          <t>Écriture</t>
+        </is>
+      </c>
+      <c r="F858" s="2" t="inlineStr">
+        <is>
+          <t>Rotring pencil</t>
+        </is>
+      </c>
+      <c r="G858" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H858" s="2" t="inlineStr"/>
+      <c r="I858" s="2" t="inlineStr"/>
+      <c r="J858" s="2" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B859" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C859" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D859" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E859" s="2" t="inlineStr">
+        <is>
+          <t>Écriture</t>
+        </is>
+      </c>
+      <c r="F859" s="2" t="inlineStr">
+        <is>
+          <t>Crayon ordinaire</t>
+        </is>
+      </c>
+      <c r="G859" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H859" s="2" t="inlineStr"/>
+      <c r="I859" s="2" t="inlineStr"/>
+      <c r="J859" s="2" t="inlineStr"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B860" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C860" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D860" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E860" s="2" t="inlineStr">
+        <is>
+          <t>Écriture</t>
+        </is>
+      </c>
+      <c r="F860" s="2" t="inlineStr">
+        <is>
+          <t>Gomme</t>
+        </is>
+      </c>
+      <c r="G860" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H860" s="2" t="inlineStr"/>
+      <c r="I860" s="2" t="inlineStr"/>
+      <c r="J860" s="2" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B861" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C861" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D861" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E861" s="2" t="inlineStr">
+        <is>
+          <t>Géométrie</t>
+        </is>
+      </c>
+      <c r="F861" s="2" t="inlineStr">
+        <is>
+          <t>Ruler 30cm</t>
+        </is>
+      </c>
+      <c r="G861" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H861" s="2" t="inlineStr"/>
+      <c r="I861" s="2" t="inlineStr"/>
+      <c r="J861" s="2" t="inlineStr"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B862" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C862" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D862" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E862" s="2" t="inlineStr">
+        <is>
+          <t>Géométrie</t>
+        </is>
+      </c>
+      <c r="F862" s="2" t="inlineStr">
+        <is>
+          <t>Mathematical set</t>
+        </is>
+      </c>
+      <c r="G862" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H862" s="2" t="inlineStr"/>
+      <c r="I862" s="2" t="inlineStr"/>
+      <c r="J862" s="2" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B863" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C863" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D863" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E863" s="2" t="inlineStr">
+        <is>
+          <t>Géométrie</t>
+        </is>
+      </c>
+      <c r="F863" s="2" t="inlineStr">
+        <is>
+          <t>Scientific calculator</t>
+        </is>
+      </c>
+      <c r="G863" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H863" s="2" t="inlineStr"/>
+      <c r="I863" s="2" t="inlineStr"/>
+      <c r="J863" s="2" t="inlineStr"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B864" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C864" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D864" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E864" s="2" t="inlineStr">
+        <is>
+          <t>Dictionnaire</t>
+        </is>
+      </c>
+      <c r="F864" s="2" t="inlineStr">
+        <is>
+          <t>English dictionary</t>
+        </is>
+      </c>
+      <c r="G864" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H864" s="2" t="inlineStr"/>
+      <c r="I864" s="2" t="inlineStr"/>
+      <c r="J864" s="2" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="B865" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="C865" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="D865" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="E865" s="2" t="inlineStr">
+        <is>
+          <t>Dictionnaire</t>
+        </is>
+      </c>
+      <c r="F865" s="2" t="inlineStr">
+        <is>
+          <t>French dictionary</t>
+        </is>
+      </c>
+      <c r="G865" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H865" s="2" t="inlineStr"/>
+      <c r="I865" s="2" t="inlineStr"/>
+      <c r="J865" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J837"/>
+  <autoFilter ref="A1:J865"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32528,7 +33592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -32574,7 +33638,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SIL Ord</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -32602,7 +33666,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>CP Ord</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -32630,7 +33694,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CE1 Ord</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -32658,7 +33722,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CE2 Ord</t>
+          <t>CE2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -32686,7 +33750,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CM1 Ord</t>
+          <t>CM1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -32714,7 +33778,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CM2 Ord</t>
+          <t>CM2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -33065,7 +34129,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -33093,7 +34157,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -33121,7 +34185,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -33149,7 +34213,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
@@ -33177,7 +34241,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -33205,7 +34269,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
@@ -33233,7 +34297,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
@@ -33261,7 +34325,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
@@ -33289,7 +34353,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
@@ -33317,7 +34381,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Collège</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
@@ -33345,7 +34409,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
@@ -33373,7 +34437,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
@@ -33401,7 +34465,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
@@ -33414,7 +34478,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Lower/Upper Sixth</t>
+          <t>Lower Sixth</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -33429,13 +34493,41 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Lycée</t>
+          <t>Secondaire</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
         <v>28</v>
       </c>
       <c r="F32" s="2" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Upper Sixth</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Cameroun</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>anglophone</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Secondaire</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F33" s="2" t="n">
         <v>33</v>
       </c>
     </row>
@@ -36272,10 +37364,10 @@
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
     </row>
@@ -36593,10 +37685,10 @@
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
     </row>
@@ -36643,10 +37735,10 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
     </row>
@@ -36768,10 +37860,10 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G137" s="2" t="inlineStr"/>
     </row>
@@ -37069,10 +38161,10 @@
       <c r="C150" s="2" t="inlineStr"/>
       <c r="D150" s="2" t="inlineStr"/>
       <c r="E150" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G150" s="2" t="inlineStr"/>
     </row>
@@ -37090,10 +38182,10 @@
       <c r="C151" s="2" t="inlineStr"/>
       <c r="D151" s="2" t="inlineStr"/>
       <c r="E151" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G151" s="2" t="inlineStr"/>
     </row>
@@ -37216,10 +38308,10 @@
       <c r="C157" s="2" t="inlineStr"/>
       <c r="D157" s="2" t="inlineStr"/>
       <c r="E157" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G157" s="2" t="inlineStr"/>
     </row>
@@ -37300,10 +38392,10 @@
       <c r="C161" s="2" t="inlineStr"/>
       <c r="D161" s="2" t="inlineStr"/>
       <c r="E161" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G161" s="2" t="inlineStr"/>
     </row>
@@ -37879,10 +38971,10 @@
       <c r="C188" s="2" t="inlineStr"/>
       <c r="D188" s="2" t="inlineStr"/>
       <c r="E188" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G188" s="2" t="inlineStr"/>
     </row>
@@ -37921,10 +39013,10 @@
       <c r="C190" s="2" t="inlineStr"/>
       <c r="D190" s="2" t="inlineStr"/>
       <c r="E190" s="3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G190" s="2" t="inlineStr"/>
     </row>
@@ -37942,10 +39034,10 @@
       <c r="C191" s="2" t="inlineStr"/>
       <c r="D191" s="2" t="inlineStr"/>
       <c r="E191" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G191" s="2" t="inlineStr"/>
     </row>
@@ -37963,10 +39055,10 @@
       <c r="C192" s="2" t="inlineStr"/>
       <c r="D192" s="2" t="inlineStr"/>
       <c r="E192" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G192" s="2" t="inlineStr"/>
     </row>
@@ -38278,10 +39370,10 @@
       <c r="C207" s="2" t="inlineStr"/>
       <c r="D207" s="2" t="inlineStr"/>
       <c r="E207" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G207" s="2" t="inlineStr"/>
     </row>
@@ -38341,10 +39433,10 @@
       <c r="C210" s="2" t="inlineStr"/>
       <c r="D210" s="2" t="inlineStr"/>
       <c r="E210" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G210" s="2" t="inlineStr"/>
     </row>
@@ -38404,10 +39496,10 @@
       <c r="C213" s="2" t="inlineStr"/>
       <c r="D213" s="2" t="inlineStr"/>
       <c r="E213" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G213" s="2" t="inlineStr"/>
     </row>
